--- a/AAII_Financials/Quarterly/VFC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VFC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>VFC</t>
   </si>
@@ -656,539 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44562</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44191</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1669400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2166000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2875800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2802700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1760700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2143800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2833900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2757900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1769100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2247300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2780200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2920100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1968100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2739600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3530700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3080600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2261600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2824700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3624400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3198200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2194600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2582700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2971500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2608300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1076300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1439100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3155700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3179800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2050700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1682700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3227700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3219400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2137100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3045400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3361100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3508800</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2359600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2500300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2743500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>3327700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>752300</v>
+      </c>
+      <c r="E9" s="3">
         <v>937600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1247500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1340300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>807400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>999800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1238700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1317400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>863000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1172100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1257000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1430200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>939600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1376800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1592300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1496200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1041600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1358700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1592500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1479300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>954200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1232100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1322500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1279200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>493000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>539800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2851900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3052600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1931000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2202100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3337700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3494100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2385600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1504000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1617900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1750800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1187400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1243900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1362400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1692600</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>917100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1228400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1628300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1462400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>953200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1143900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1595200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1440600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>906000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1075200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1523200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1489900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1028400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1362800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1938400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1584400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1220000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1466000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2031900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1718900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1240400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1350600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1649000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1329100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>583300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>899300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>303800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>127200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>119700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-519400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-110000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-274700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-248500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1541400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1743200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1758000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1172200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1256400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1381100</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1635100</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,8 +1244,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1353,8 +1367,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1475,175 +1492,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E14" s="3">
         <v>52100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>60900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>17500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>93400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>67400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>309400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>278900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>467700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>4300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>55400</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>38200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>23400</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>22500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>407100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>28800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>131000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>77500</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>57800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>14900</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>104700</v>
-      </c>
-      <c r="AM14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP14" s="3">
         <v>79600</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E15" s="3">
         <v>67000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>78900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>69500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>64400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>72800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>60000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>61800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>63700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>84800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>85800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>69900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>67100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>69400</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1719,8 +1742,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1761700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2084700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2560800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2486400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1830100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2139900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2541400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2473400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1879300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2311300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2563400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2569100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2601200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3015300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3171400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2198200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2632300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2949600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2639700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1991700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2460200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2559500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2288400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1323100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1864200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2615700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2631200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1954700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1671400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2712100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2706700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2024000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2734100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2801500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3024900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2191600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2210700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2489800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2719500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-92300</v>
+      </c>
+      <c r="E18" s="3">
         <v>81400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>315000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>316300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-69500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>292500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>284600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-110300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-64000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>216800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>351100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-32500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>138500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>515400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-90800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>63400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>192400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>674800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>558500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>202900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>122500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>412000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>319900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-246800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-425100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>540000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>548600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>96000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>515600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>512700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>113100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>311300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>559600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>483900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>168000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>289600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>253700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>608200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2048,618 +2081,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>165800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-143400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-93400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>10400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>9100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>11100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>9100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>7800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-36900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-46100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>5100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>23400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>34200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>7300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-17200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>7200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>5800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>4300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>1900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>3500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>3100</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-17400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>537300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>388900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>78700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>360600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>346900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-46700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>302500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>418700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>34300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>202700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>571600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-35400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>36700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>270100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>740400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>634100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>282100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>191500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>486700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>403600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-220700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-407900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>428400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>734000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>289400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>121800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>585700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>590900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>148700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>390100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>648300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>563900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>235400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>359500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>332900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>677400</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E22" s="3">
         <v>33800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>39700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>49600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>43600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>40100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>43300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>46400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>44300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>46900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>52700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>45700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>40700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>53000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>54100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>34700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>32500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>31700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>34000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>35900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>34900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>38000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>34300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>34100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>29300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>26800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>44600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>41600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>44300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24100</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>28300</v>
       </c>
       <c r="AH22" s="3">
         <v>28300</v>
       </c>
       <c r="AI22" s="3">
+        <v>28300</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>27000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>24400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>27000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>27100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>24200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>23700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>24300</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>24800</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-106900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-163300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>362900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>268300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-126600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-116600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>196700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>230600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-165500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-411800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-111300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>307200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-69100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-216000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>455900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-134000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-62600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>171100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>641300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>531700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>179200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>89000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>386700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>293700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-312900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-497900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>500600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>530400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>85900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>494600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>486200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>68800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>294100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>538400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>461100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>145800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>269400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>232500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>584600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-44000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>62000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>78500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-10200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>33700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>27600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-13400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-19600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>758900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-6100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>42900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-15600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-6700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>90700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>123500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>67600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>25200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>27300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>59000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>50400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-35200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>165500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>79000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-95000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>20700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>75100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>54300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>38100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>68000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>74300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>30900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>56100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>17300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>99400</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2780,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-97200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-119300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>300800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>189800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-116400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-150300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>169100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>202500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-152000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-412100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-91700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-451600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-63000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-214900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>413000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-118400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-56000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>80400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>517800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>464100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>154000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>61700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>327700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>243200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-277700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-663400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>421600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>625400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>65300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>419500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>431900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>58500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>256100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>470400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>386800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>114900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>213300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>215200</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>485200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-97200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-119300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>300800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>189800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-116400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-150800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>167800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>52200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-258900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-418300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-42500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-450700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-57400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-214900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>413000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-118400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-56000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>80400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>517800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>464100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>154000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>61700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>327700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>243200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-277700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-663400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>421600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>625400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>65300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>419500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>431900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>58500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>256100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>470400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>386800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>114900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>213300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>215200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>485200</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3146,8 +3204,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3164,112 +3225,115 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-500</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-1300</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-150300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-106900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-6200</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>49300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>900</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>5600</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>94900</v>
       </c>
-      <c r="R29" s="3" t="s">
+      <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>400</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>170300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>27800</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>19600</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>13500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-7900</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>179700</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>43400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>23600</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-16100</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>131100</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>44000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>75200</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>101900</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>-3300</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-560700</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-600</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-4100</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>49100</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>13300</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3390,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3512,252 +3579,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-165800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>143400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>93400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-10400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-9100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-11100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>36900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>46100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-23400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-34200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-7300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-7200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-5800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-97200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-119300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>300800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>189800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-116400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-150800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>167800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>52200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-258900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-418300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-42500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-450700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-57400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-214900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>507900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-118400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-56000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>80800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>517800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>464100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>324200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>89500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>347200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>256700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-285600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-483800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>465000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>649000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>49200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>128800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>463500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>507100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>160400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>252800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-90300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>386100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>109900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>209200</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>264300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>498500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3878,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-97200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-119300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>300800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>189800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-116400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-150800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>167800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>52200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-258900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-418300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-42500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-450700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-57400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-214900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>507900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-118400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-56000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>80800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>517800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>464100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>324200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>89500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>347200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>256700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-285600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-483800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>465000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>649000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>49200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>128800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>463500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>507100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>160400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>252800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-90300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>386100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>109900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>209200</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>264300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>498500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44562</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44191</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4171,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4215,130 +4301,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>670100</v>
+      </c>
+      <c r="E41" s="3">
         <v>823900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1466500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>419100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>642400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>429400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1369400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>492200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>637400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>656400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>988000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>498900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>806500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>814900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>571300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>552800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>528000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1275900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1333800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1360100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1274900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>815800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3254200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1877400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2145100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1369000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>584000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>507600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>606100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>445100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>535300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>352800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>467900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>680800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>563500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1546100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>672500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>603300</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1227900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>737800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4361,20 +4451,20 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1700</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>1700</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -4400,22 +4490,22 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
-        <v>598800</v>
+        <v>0</v>
       </c>
       <c r="X42" s="3">
         <v>598800</v>
       </c>
       <c r="Y42" s="3">
+        <v>598800</v>
+      </c>
+      <c r="Z42" s="3">
         <v>599400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>800000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>700000</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC42" s="3" t="s">
         <v>8</v>
@@ -4432,8 +4522,8 @@
       <c r="AG42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH42" s="3">
-        <v>0</v>
+      <c r="AH42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI42" s="3">
         <v>0</v>
@@ -4459,504 +4549,519 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1216400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1448500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1417900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1884000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1178600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1352200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1345000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1824600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1058800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1291400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1351000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1893100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1216900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1656300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1566200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1837400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1251700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1468900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1497300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1789100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1139900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1298900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1413100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1609100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>937500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1309200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1643500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1978600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1307800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1468400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1777800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2199400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1431500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1408600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1430000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1851400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1155700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1241500</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1148800</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1785300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1899500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1371300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1658700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1855900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2135500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1627000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1794500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2082900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2110600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1697800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2148200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2481100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2787000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2292800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2591900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2749900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2341400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1418700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1287200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1464700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1216800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1061800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1076000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1434800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1402900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1293900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1565000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1890700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1665100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1432700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1866100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2247900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1993800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1861400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1706600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1909600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1713000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1593400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1424600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2000000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>406400</v>
+      </c>
+      <c r="E45" s="3">
         <v>261200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>426000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>948600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>413200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>273400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>512500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2056700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>538300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>472100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>445800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>369300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>401700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>280500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>514500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>548200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>490500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>424600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>482300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>355900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>333600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1010600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>942500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>958900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1075700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1054800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>363200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>398300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>411800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1327300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>432900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>617800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>436900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>732500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>677700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>320300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>356500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>654000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>491900</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>295900</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4202600</v>
+      </c>
+      <c r="E46" s="3">
         <v>4009500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4982100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5118900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4375500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3786100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5021500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6458900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4349100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4226900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4935900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5243600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5213600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5152700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5244000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5688200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4611700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4588100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4600600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4969900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4564100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4785900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>7285200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6680200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6261100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5027000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4155700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4775200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3990900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4673500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4612100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5418000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4330100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4683300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4377800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5627400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3897700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4092200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4293100</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4819000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>43900</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>8</v>
@@ -4964,11 +5069,11 @@
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>38500</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
@@ -4976,24 +5081,24 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3">
         <v>39800</v>
       </c>
-      <c r="M47" s="3" t="s">
+      <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>27500</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5069,252 +5174,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1981900</v>
+      </c>
+      <c r="E48" s="3">
         <v>1995200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2051900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2035600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2039900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1983200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1986900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2068800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2127200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2044100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2227700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2224200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2292900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2314600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2225700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2201300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2235300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2288800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2352200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2391500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2443200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2450300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2432300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2319100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2311600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2227900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2207400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2135500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2146200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>915200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1041600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1035700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1018200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1011600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1014600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>921200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>919000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>897400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1822000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>949300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2049500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2274800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2066300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2096500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2344600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2568400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2341100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2426600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3932500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2709700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4360400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4592000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4614400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4970000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4932900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4878700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5343700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5394200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5419800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5434000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5455200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5455000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3056300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3024600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3018400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3010600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3487800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3449200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3525100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3765400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3812100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3846900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>4000400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3813300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>4049900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3579400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3631700</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>4924300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5003000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>3769300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5435,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5557,130 +5674,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1230500</v>
+      </c>
+      <c r="E52" s="3">
         <v>303600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1331300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1393200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1390500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>394900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1204700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1265300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1132500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2088900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1092500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1077700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1918400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1405800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1910700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1015900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1021000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1071100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1163700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1093700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1087800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1062900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>970500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>917300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>887900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>867800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>963400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>910500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>739800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1254500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>818500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>829900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>843000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>803000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>783700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>746900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>725400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1146500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1461600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>905500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5801,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9464400</v>
+      </c>
+      <c r="E54" s="3">
         <v>9290200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10431600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10644100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10150500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9377500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10554200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12219600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11541400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11613000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12616500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13142400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14043900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13990500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14313300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13784100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13211800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13342200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13536300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13889100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13550400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13754000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13744300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12941300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12479000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11133300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10814300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11270400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10402000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10356800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10284300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11130400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>10191800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>10311300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9958500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>10874900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>9173700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9246300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>9739300</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>10443100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5967,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6011,740 +6141,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1274700</v>
+      </c>
+      <c r="E57" s="3">
         <v>826300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1014400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1061000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1166800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>789600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1007800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1134600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1157800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>788500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>974800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>992900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1282300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>936300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>906300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1022400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1022800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>563000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>559700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>534400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>534800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>463200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>412300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>450100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>348900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>407000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>457000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>550700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>588400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>580900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>645700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>732500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>675600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>583000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>761000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>554100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>502900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>425900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>620200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>565700</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>834500</v>
+      </c>
+      <c r="E58" s="3">
         <v>343600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>598700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1086100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>978900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>861200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>763300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2213300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2013300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1559700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1452900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1024200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>987300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1268000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1812300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2524900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>828400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>836500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>606900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1011200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1009100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>12100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>300800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>14400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>20300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1229800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>60700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>489300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>72700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>669600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>683500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1576400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1323100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1531400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>741700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2239100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1174900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>542400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>279700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>741300</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>136400</v>
+      </c>
+      <c r="E59" s="3">
         <v>259700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>175000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>261800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>236200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>272100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>146700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>313600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>80100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>357400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>167900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>56000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>102200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>491100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1827600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1798700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1612800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1915900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2057200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1838800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1527500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1735200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1784900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1620100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1346300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1387000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1444400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1364300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1286000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1416400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1233900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1199800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>996900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1024500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1247600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1028200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>753300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>867600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>885500</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>870100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2948400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2181200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3217100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3758700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3439600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2697900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3226900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4982400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4409000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3457000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3997300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3544800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3816400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3545800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4546200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5346000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3464000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3315400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3223900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3384400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3071400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2210500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2498000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2084500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1715500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3023900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1962100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2404300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1947100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2661600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2563000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3508700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2995600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3138800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2744100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3821400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2431100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1835900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1785400</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2177200</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4119200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4639700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4740000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4705000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4696100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4504800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4988200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5165200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5108100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5789600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5889000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6778400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6878300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6884100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4617400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3526100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4468400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4584300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4646400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4682800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4726200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5709100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5786600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5679400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5609800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2608300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2110500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2090900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2126800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2115900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2135200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2150600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2156600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2212600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2187800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2144200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2111600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>2051500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2039200</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2347100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>632100</v>
+      </c>
+      <c r="E62" s="3">
         <v>525300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>690100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>702500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>722500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>595300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>658900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>665700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>636400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>619400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>621000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>609100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>632400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>469500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1830000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1826400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1926900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1912200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2012700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2223500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2478600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2778200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2321600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2232100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2241200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2143800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2174100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2127500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2176400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1280800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1285400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1291600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1308500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1271800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1306700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>971900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>986600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>985900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>973800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1046000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6865,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6987,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7109,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7699800</v>
+      </c>
+      <c r="E66" s="3">
         <v>7440300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8647200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9166300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8858200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7890200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8874000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10813300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10153500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9954600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10507300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10932300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11327100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11079800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10993700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10698500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9859300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9811900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9882900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10290600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10276300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10697900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10606200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9996000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9566400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7775900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6246700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6622700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6250400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6058300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5983700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6950900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6460600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6623200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6238600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6937500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5529400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4873200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4798400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>5570300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7397,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7519,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7641,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7763,130 +7934,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1037100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-928800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-808200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1107000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1295300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1173000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1020400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1185600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1235900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-974600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-556300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-513500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-60700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>57100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>385800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-120100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>188800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>443500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>608700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>586400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>317100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>189500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>300500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-45000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-298100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1182200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1406000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>931100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1179600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1258300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1147800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>825800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>846100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1023700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1297000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1077700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1892300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2545500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2454300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8007,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8129,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8251,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1764600</v>
+      </c>
+      <c r="E76" s="3">
         <v>1849900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1784400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1477900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1292300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1487400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1680200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1406400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1387900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1658400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2109200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2210000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2716800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2910700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3319600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3085600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3352500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3530400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3653400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3598500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3274000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3056200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3138200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2945200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2912600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3357300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4567600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4647600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4151600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4298500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4300600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4179600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3731100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3688100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3719900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3937400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3644300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4373100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4940900</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4872800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44562</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44191</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-97200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-119300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>300800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>189800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-116400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-150800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>167800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>52200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-258900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-418300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-42500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-450700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-57400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-214900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>507900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-118400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-56000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>80800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>517800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>464100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>324200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>89500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>347200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>256700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-285600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-483800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>465000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>649000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>49200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>128800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>463500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>507100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>160400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>252800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-90300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>386100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>109900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>209200</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>264300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>498500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E83" s="3">
         <v>59600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>60000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>61800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>63700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>71000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>85800</v>
       </c>
-      <c r="J83" s="3" t="s">
+      <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>67100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>55300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>61500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>60300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>63100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>59300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>61600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>63900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>66800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>67300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>65100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>66500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>68100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>64500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>65700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>75800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>63000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>63300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>-116800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>162000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>159200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>84600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>71400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>73900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>71100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>71500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>82900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>75700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>65500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>66400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>76100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>68000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9154,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9276,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9398,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9520,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-62500</v>
+      </c>
+      <c r="E89" s="3">
         <v>33300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1010400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-227000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-145500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-171100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>918100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-301600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-91200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1125000</v>
       </c>
-      <c r="N89" s="3" t="s">
+      <c r="O89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>163600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>177700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>80500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-555600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-358300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>66900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>968500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-252100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>81000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>171200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1059200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>86000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>32900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1207100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-299300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-66200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>227600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1333700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-174200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>277100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-243200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1468000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>11200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>205600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-210200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1433400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>30600</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-27400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-32600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-26500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-28200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-22000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-22200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-21200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-20700</v>
       </c>
-      <c r="N91" s="3" t="s">
+      <c r="O91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-61800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-35700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-67900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-58300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-79600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-50300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-91300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-72500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-114200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-46200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-39900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-43300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-69200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-101900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-62300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-46300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-70400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-50700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-67100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-62500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-54400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-45200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-46200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-37400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-61500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-116600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-123600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9930,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10052,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-50600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>547700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-41100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-49000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1466900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>19700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-42300</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-90600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>18800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-75100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-62200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-69500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-49700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-98900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>543500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>508800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2078900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>140700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-172200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-785200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-128100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-96500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-76800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-72100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>69800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-89100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-129200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-56000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-801300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-64000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>157500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-68300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-61600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>50500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,13 +10451,14 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>35200</v>
+        <v>35400</v>
       </c>
       <c r="E96" s="3">
         <v>35200</v>
@@ -10236,10 +10470,10 @@
         <v>35200</v>
       </c>
       <c r="H96" s="3">
+        <v>35200</v>
+      </c>
+      <c r="I96" s="3">
         <v>35100</v>
-      </c>
-      <c r="I96" s="3">
-        <v>35000</v>
       </c>
       <c r="J96" s="3">
         <v>35000</v>
@@ -10253,95 +10487,98 @@
       <c r="M96" s="3">
         <v>35000</v>
       </c>
-      <c r="N96" s="3" t="s">
+      <c r="N96" s="3">
+        <v>35000</v>
+      </c>
+      <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>116600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>116500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-198100</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-194100</v>
       </c>
       <c r="S96" s="3">
         <v>-194100</v>
       </c>
       <c r="T96" s="3">
+        <v>-194100</v>
+      </c>
+      <c r="U96" s="3">
         <v>-194000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-194800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-192300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-192100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-191900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-191300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-186900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-186700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-186400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-188700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-171100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-202500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-201900</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-201300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-182300</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-181500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-181400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-181700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-165400</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-164900</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-172700</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-173600</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-152800</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10462,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10584,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10706,370 +10949,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-611900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-527700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>62900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>339000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-786300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1485700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>163400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-37400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-223800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-609900</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-71900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>45200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>10000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>670000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-261200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-11200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-897800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-185400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-174400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-472500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>147900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-185200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1562700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>931900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1034000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>288100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>123900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-153300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1240600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>146900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-344000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>406800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1664400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>931700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-283800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-346500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-875300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-13100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E101" s="3">
         <v>35500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-42600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>22600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-17100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>16200</v>
       </c>
-      <c r="J101" s="3" t="s">
+      <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-26900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-59000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-64000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-26900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-59000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-64000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-21000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>10000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-43100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>20600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-22500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-10500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>15500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>16600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>12200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>16900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>2200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-7600</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-7200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-151800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-647200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1044100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-212800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>216900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-939800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>856700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-125300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-37000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-312400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>489100</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-8200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>243300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>18700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>25300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-748000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-57900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-26600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>85000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>425400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2423400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1368500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-283600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>778400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>814100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>77000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-98500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>62100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>17700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>179500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-113700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-216000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>119800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-980900</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>873300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>68700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-622700</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>488800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>60600</v>
       </c>
     </row>
